--- a/KNK업무시스템구축_엑셀/V2/01_검사기_완제품/KNK_검사기_완제품_품질팀_입력_2026.xlsx
+++ b/KNK업무시스템구축_엑셀/V2/01_검사기_완제품/KNK_검사기_완제품_품질팀_입력_2026.xlsx
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>T-260407-3</t>
+          <t>T-260407-2</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>T-260303-2</t>
+          <t>T-260303-1</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>T-260409-2</t>
+          <t>T-260409-1</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>T-260409-3</t>
+          <t>T-260409-2</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>T-260410-2</t>
+          <t>T-260410-1</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>T-260410-3</t>
+          <t>T-260410-2</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>T-260403-6</t>
+          <t>T-260403-5</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>T-260408-7</t>
+          <t>T-260408-6</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>T-260408-8</t>
+          <t>T-260408-7</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>T-260408-9</t>
+          <t>T-260408-8</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>T-260408-10</t>
+          <t>T-260408-9</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>T-260406-2</t>
+          <t>T-260406-1</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>T-260406-3</t>
+          <t>T-260406-2</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>T-260406-4</t>
+          <t>T-260406-3</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>T-260406-5</t>
+          <t>T-260406-4</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>T-260406-6</t>
+          <t>T-260406-5</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>T-260406-7</t>
+          <t>T-260406-6</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>T-260406-12</t>
+          <t>T-260406-11</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>T-260406-13</t>
+          <t>T-260406-12</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>T-260406-14</t>
+          <t>T-260406-13</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>T-260406-15</t>
+          <t>T-260406-14</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>T-260327-2</t>
+          <t>T-260327-1</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>T-260327-3</t>
+          <t>T-260327-2</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>T-260327-4</t>
+          <t>T-260327-3</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>T-260327-5</t>
+          <t>T-260327-4</t>
         </is>
       </c>
       <c r="D33" s="8" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>T-260327-6</t>
+          <t>T-260327-5</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>T-260327-7</t>
+          <t>T-260327-6</t>
         </is>
       </c>
       <c r="D35" s="8" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>T-260331-2</t>
+          <t>T-260331-1</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>T-260324-5</t>
+          <t>T-260324-4</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>T-260401-4</t>
+          <t>T-260401-3</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>T-260323-2</t>
+          <t>T-260323-1</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>T-260323-3</t>
+          <t>T-260323-2</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>T-260323-4</t>
+          <t>T-260323-3</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>T-260323-5</t>
+          <t>T-260323-4</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>T-260323-6</t>
+          <t>T-260323-5</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>T-260406-16</t>
+          <t>T-260406-15</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>T-260408-2</t>
+          <t>T-260408-1</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>T-260408-3</t>
+          <t>T-260408-2</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>T-260408-4</t>
+          <t>T-260408-3</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>T-260406-8</t>
+          <t>T-260406-7</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>T-260406-9</t>
+          <t>T-260406-8</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>T-260406-10</t>
+          <t>T-260406-9</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>T-260406-11</t>
+          <t>T-260406-10</t>
         </is>
       </c>
       <c r="D55" s="8" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>T-260407-2</t>
+          <t>T-260407-1</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>T-260409-4</t>
+          <t>T-260409-3</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>T-260409-5</t>
+          <t>T-260409-4</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>T-260409-6</t>
+          <t>T-260409-5</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>T-260324-8</t>
+          <t>T-260324-7</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>T-260407-4</t>
+          <t>T-260407-3</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>T-260324-10</t>
+          <t>T-260324-9</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>T-260410-4</t>
+          <t>T-260410-3</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>T-260413-2</t>
+          <t>T-260413-1</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>T-260413-3</t>
+          <t>T-260413-2</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>T-260413-4</t>
+          <t>T-260413-3</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>T-260413-5</t>
+          <t>T-260413-4</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>T-260409-7</t>
+          <t>T-260409-6</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>T-260409-8</t>
+          <t>T-260409-7</t>
         </is>
       </c>
       <c r="D71" s="8" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>T-260409-9</t>
+          <t>T-260409-8</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>T-260409-10</t>
+          <t>T-260409-9</t>
         </is>
       </c>
       <c r="D73" s="8" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>T-260409-11</t>
+          <t>T-260409-10</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>T-260407-5</t>
+          <t>T-260407-4</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>T-260413-6</t>
+          <t>T-260413-5</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>T-260413-7</t>
+          <t>T-260413-6</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>T-260413-8</t>
+          <t>T-260413-7</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>T-260413-9</t>
+          <t>T-260413-8</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>T-260413-10</t>
+          <t>T-260413-9</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>T-260413-11</t>
+          <t>T-260413-10</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>T-260331-3</t>
+          <t>T-260331-2</t>
         </is>
       </c>
       <c r="D83" s="8" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>T-260324-9</t>
+          <t>T-260324-8</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>T-260413-12</t>
+          <t>T-260413-11</t>
         </is>
       </c>
       <c r="D87" s="8" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>T-260413-17</t>
+          <t>T-260413-16</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>T-260413-18</t>
+          <t>T-260413-17</t>
         </is>
       </c>
       <c r="D89" s="8" t="inlineStr">
@@ -5543,7 +5543,7 @@
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>T-260413-19</t>
+          <t>T-260413-18</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>T-260415-2</t>
+          <t>T-260415-1</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -5699,7 +5699,7 @@
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>T-260415-3</t>
+          <t>T-260415-2</t>
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>T-260413-13</t>
+          <t>T-260413-12</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>T-260413-14</t>
+          <t>T-260413-13</t>
         </is>
       </c>
       <c r="D95" s="8" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>T-260413-15</t>
+          <t>T-260413-14</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>T-260413-16</t>
+          <t>T-260413-15</t>
         </is>
       </c>
       <c r="D97" s="8" t="inlineStr">
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>T-260408-5</t>
+          <t>T-260408-4</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>T-260408-6</t>
+          <t>T-260408-5</t>
         </is>
       </c>
       <c r="D99" s="8" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>T-260414-2</t>
+          <t>T-260414-1</t>
         </is>
       </c>
       <c r="D101" s="8" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>T-260413-20</t>
+          <t>T-260413-19</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -6219,7 +6219,7 @@
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>T-260413-21</t>
+          <t>T-260413-20</t>
         </is>
       </c>
       <c r="D103" s="8" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>T-260414-3</t>
+          <t>T-260414-2</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>T-260226-2</t>
+          <t>T-260226-1</t>
         </is>
       </c>
       <c r="D105" s="8" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>T-260226-3</t>
+          <t>T-260226-2</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>T-260331-12</t>
+          <t>T-260331-11</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>T-260425-2</t>
+          <t>T-260425-1</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
